--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92557090632</v>
+        <v>46157.93118945717</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118945717</v>
+        <v>46157.93140700779</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93140700779</v>
+        <v>46157.93387165837</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93387165837</v>
+        <v>46157.93699096137</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93699096137</v>
+        <v>46158.28206562781</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28206562781</v>
+        <v>46158.29656038373</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29656038373</v>
+        <v>46158.29795856591</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29795856591</v>
+        <v>46158.33373247472</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33373247472</v>
+        <v>46158.37226952059</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Январь 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37226952059</v>
+        <v>46158.37277204234</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
